--- a/finance/_refresh_caribbean.xlsx
+++ b/finance/_refresh_caribbean.xlsx
@@ -2369,19 +2369,9 @@
         <f>((D4*O4/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D4*O4*VLOOKUP(B4,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG4" s="31" t="n">
-        <v>27418</v>
-      </c>
-      <c r="AH4" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI4" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="AG4" s="31" t="n"/>
+      <c r="AH4" s="32" t="n"/>
+      <c r="AI4" s="32" t="n"/>
       <c r="AJ4" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -2431,11 +2421,7 @@
           <t>MODELED dive-transfer band (Klein Bonaire). To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY4" s="44" t="inlineStr">
-        <is>
-          <t>bonaire dive transfer pool</t>
-        </is>
-      </c>
+      <c r="AY4" s="44" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
@@ -2568,19 +2554,9 @@
         <f>((D5*O5/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D5*O5*VLOOKUP(B5,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG5" s="31" t="n">
-        <v>53850</v>
-      </c>
-      <c r="AH5" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI5" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="AG5" s="31" t="n"/>
+      <c r="AH5" s="32" t="n"/>
+      <c r="AI5" s="32" t="n"/>
       <c r="AJ5" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -2630,11 +2606,7 @@
           <t>MODELED short town/cruise→dive-resort transfer. To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY5" s="44" t="inlineStr">
-        <is>
-          <t>bonaire cruise → dive-resort cluster</t>
-        </is>
-      </c>
+      <c r="AY5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -2767,19 +2739,9 @@
         <f>((D6*O6/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D6*O6*VLOOKUP(B6,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG6" s="31" t="n">
-        <v>216000</v>
-      </c>
-      <c r="AH6" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI6" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="AG6" s="31" t="n"/>
+      <c r="AH6" s="32" t="n"/>
+      <c r="AI6" s="32" t="n"/>
       <c r="AJ6" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -2829,11 +2791,7 @@
           <t>MODELED premium air→resort transfer band. To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY6" s="44" t="inlineStr">
-        <is>
-          <t>aruba airport → resort</t>
-        </is>
-      </c>
+      <c r="AY6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -2966,19 +2924,9 @@
         <f>((D7*O7/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D7*O7*VLOOKUP(B7,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG7" s="31" t="n">
-        <v>102000</v>
-      </c>
-      <c r="AH7" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI7" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="AG7" s="31" t="n"/>
+      <c r="AH7" s="32" t="n"/>
+      <c r="AI7" s="32" t="n"/>
       <c r="AJ7" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3028,11 +2976,7 @@
           <t>MODELED premium cruise-shore / resort transfer band. To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY7" s="44" t="inlineStr">
-        <is>
-          <t>aruba cruise → resort strip</t>
-        </is>
-      </c>
+      <c r="AY7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -3165,19 +3109,9 @@
         <f>((D8*O8/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D8*O8*VLOOKUP(B8,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG8" s="31" t="n">
-        <v>83489</v>
-      </c>
-      <c r="AH8" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI8" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="AG8" s="31" t="n"/>
+      <c r="AH8" s="32" t="n"/>
+      <c r="AI8" s="32" t="n"/>
       <c r="AJ8" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3227,11 +3161,7 @@
           <t>MODELED premium cruise/town→resort transfer band. To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY8" s="44" t="inlineStr">
-        <is>
-          <t>curacao cruise → resort cluster</t>
-        </is>
-      </c>
+      <c r="AY8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -3364,19 +3294,9 @@
         <f>((D9*O9/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D9*O9*VLOOKUP(B9,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG9" s="31" t="n">
-        <v>84029</v>
-      </c>
-      <c r="AH9" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI9" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="AG9" s="31" t="n"/>
+      <c r="AH9" s="32" t="n"/>
+      <c r="AI9" s="32" t="n"/>
       <c r="AJ9" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3426,11 +3346,7 @@
           <t>MODELED premium air→resort transfer band. To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY9" s="44" t="inlineStr">
-        <is>
-          <t>curacao airport → south-coast resorts</t>
-        </is>
-      </c>
+      <c r="AY9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -3563,19 +3479,9 @@
         <f>((D10*O10/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D10*O10*VLOOKUP(B10,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG10" s="31" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AH10" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI10" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="AG10" s="31" t="n"/>
+      <c r="AH10" s="32" t="n"/>
+      <c r="AI10" s="32" t="n"/>
       <c r="AJ10" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3625,11 +3531,7 @@
           <t>MODELED premium seasonal excursion. To be finalized in cascade with season_days.</t>
         </is>
       </c>
-      <c r="AY10" s="44" t="inlineStr">
-        <is>
-          <t>ABC broad-footprint default slice</t>
-        </is>
-      </c>
+      <c r="AY10" s="44" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -3762,19 +3664,9 @@
         <f>((D11*O11/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D11*O11*VLOOKUP(B11,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG11" s="31" t="n">
-        <v>55480</v>
-      </c>
-      <c r="AH11" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI11" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="AG11" s="31" t="n"/>
+      <c r="AH11" s="32" t="n"/>
+      <c r="AI11" s="32" t="n"/>
       <c r="AJ11" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3824,11 +3716,7 @@
           <t>MODELED against the live Divi Divi/EZ Air Curaçao↔Bonaire one-way fare band (~$90-130); sea transfer priced below air. To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY11" s="44" t="inlineStr">
-        <is>
-          <t>inter_island_air_substitution_pool Curaçao↔Bonaire high-frequency turboprop</t>
-        </is>
-      </c>
+      <c r="AY11" s="44" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">

--- a/finance/_refresh_caribbean.xlsx
+++ b/finance/_refresh_caribbean.xlsx
@@ -44,7 +44,7 @@
     <definedName name="scenario">'Assumptions'!$B$38</definedName>
     <definedName name="load_sel">'Assumptions'!$B$39</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
-    <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
+    <definedName name="country_opex">'Country opex'!$A$4:$G$6</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$17</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$17</definedName>
   </definedNames>
@@ -1798,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1863,30 +1863,90 @@
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B4" s="26" t="n">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="C4" s="27" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G4" s="26" t="n">
         <v>600000</v>
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>Modeled SG marine crew ~SGD 4-5k/mo blended | SG regulated tariff 28.1c SGD = $0.21 | SG high-cost berth modeled | CAPEX LB-243 US/EU=$900K else $600K</t>
+          <t>Modeled. Dutch-Caribbean tourism economy (GDP/cap ~$30k); AWG pegged to USD. Blended 1 commercial tourism-boat captain + deckhand fully-loaded ~$40k/vessel/yr. Above Latin America, below French Polynesia's French-territory social charges ($55k). | Dutch govt report: ABC commercial electricity US$0.35-0.38/kWh despite subsidies. WEB Aruba fuel-oil + Vader Piet wind. Anchored $0.35. | Modeled berth+insurance+admin/vessel/yr. Renaissance Marina / Palm Beach premium island ops; ~= French Polynesia $18k. | CAPEX LB-243 US/EU=$900K else $600K</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Bonaire</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>Modeled. Special municipality of the Netherlands; uses USD. Smaller dive-led economy; blended captain+deckhand ~$38k/vessel/yr, just below Aruba/Curacao. | Dutch govt report $0.35-0.38/kWh; ACM-NL regulated. ContourGlobal diesel + high wind share. Anchored $0.35. | Modeled. Kralendijk + dive-resort jetties; smaller-scale than Aruba/Curacao premium marinas. | CAPEX LB-243 US/EU=$900K else $600K</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Modeled. ANG pegged to USD; tourism+refinery economy. Blended captain+deckhand ~$40k/vessel/yr, ~= Aruba. | Dutch govt report $0.35-0.38/kWh. Aqualectra fuel-oil + Tera Kora/Playa Kanoa wind; Aqualectra raising renewable share. Anchored $0.35. | Modeled. Spanish Water (Caracasbaai) + Willemstad premium island ops. | CAPEX LB-243 US/EU=$900K else $600K</t>
         </is>
       </c>
     </row>
@@ -2246,19 +2306,19 @@
       </c>
       <c r="B4" s="29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C4" s="30" t="inlineStr">
         <is>
-          <t>Kralendijk Town Pier (Bonaire) → Klein Bonaire dive transfer (Bonaire National Marine Park)</t>
+          <t>Queen Beatrix Airport waterfront (Aruba) → Palm Beach resort strip (Aruba)</t>
         </is>
       </c>
       <c r="D4" s="31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F4" s="32" t="inlineStr">
         <is>
@@ -2271,7 +2331,7 @@
         </is>
       </c>
       <c r="H4" s="19" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="I4" s="33">
         <f>60*D4/cruise_kt</f>
@@ -2369,11 +2429,21 @@
         <f>((D4*O4/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D4*O4*VLOOKUP(B4,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG4" s="31" t="n"/>
-      <c r="AH4" s="32" t="n"/>
-      <c r="AI4" s="32" t="n"/>
+      <c r="AG4" s="31" t="n">
+        <v>216000</v>
+      </c>
+      <c r="AH4" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI4" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="AJ4" s="39" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="AK4" s="34">
         <f>IF(AG4="","",AG4*AJ4)</f>
@@ -2418,10 +2488,14 @@
       </c>
       <c r="AX4" s="44" t="inlineStr">
         <is>
-          <t>MODELED dive-transfer band (Klein Bonaire). To be finalized in cascade.</t>
-        </is>
-      </c>
-      <c r="AY4" s="44" t="n"/>
+          <t>MODELED premium air→resort transfer band. To be finalized in cascade.</t>
+        </is>
+      </c>
+      <c r="AY4" s="44" t="inlineStr">
+        <is>
+          <t>aruba airport → resort</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
@@ -2431,19 +2505,19 @@
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>Kralendijk Town Pier (Bonaire) → Harbour Village Marina / dive-resort jetty cluster (Bonaire)</t>
+          <t>Oranjestad Cruise Terminal (Aruba) → Palm Beach resort strip (Aruba)</t>
         </is>
       </c>
       <c r="D5" s="31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F5" s="32" t="inlineStr">
         <is>
@@ -2456,7 +2530,7 @@
         </is>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="I5" s="33">
         <f>60*D5/cruise_kt</f>
@@ -2554,11 +2628,21 @@
         <f>((D5*O5/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D5*O5*VLOOKUP(B5,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG5" s="31" t="n"/>
-      <c r="AH5" s="32" t="n"/>
-      <c r="AI5" s="32" t="n"/>
+      <c r="AG5" s="31" t="n">
+        <v>102000</v>
+      </c>
+      <c r="AH5" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI5" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="AJ5" s="39" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="AK5" s="34">
         <f>IF(AG5="","",AG5*AJ5)</f>
@@ -2603,10 +2687,14 @@
       </c>
       <c r="AX5" s="44" t="inlineStr">
         <is>
-          <t>MODELED short town/cruise→dive-resort transfer. To be finalized in cascade.</t>
-        </is>
-      </c>
-      <c r="AY5" s="44" t="n"/>
+          <t>MODELED premium cruise-shore / resort transfer band. To be finalized in cascade.</t>
+        </is>
+      </c>
+      <c r="AY5" s="44" t="inlineStr">
+        <is>
+          <t>aruba cruise → resort strip</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -2616,19 +2704,19 @@
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Bonaire</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>Queen Beatrix Airport waterfront (Aruba) → Palm Beach resort strip (Aruba)</t>
+          <t>Kralendijk Town Pier (Bonaire) → Klein Bonaire dive transfer (Bonaire National Marine Park)</t>
         </is>
       </c>
       <c r="D6" s="31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F6" s="32" t="inlineStr">
         <is>
@@ -2641,7 +2729,7 @@
         </is>
       </c>
       <c r="H6" s="19" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="I6" s="33">
         <f>60*D6/cruise_kt</f>
@@ -2739,11 +2827,21 @@
         <f>((D6*O6/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D6*O6*VLOOKUP(B6,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG6" s="31" t="n"/>
-      <c r="AH6" s="32" t="n"/>
-      <c r="AI6" s="32" t="n"/>
+      <c r="AG6" s="31" t="n">
+        <v>27418</v>
+      </c>
+      <c r="AH6" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI6" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="AJ6" s="39" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="AK6" s="34">
         <f>IF(AG6="","",AG6*AJ6)</f>
@@ -2788,10 +2886,14 @@
       </c>
       <c r="AX6" s="44" t="inlineStr">
         <is>
-          <t>MODELED premium air→resort transfer band. To be finalized in cascade.</t>
-        </is>
-      </c>
-      <c r="AY6" s="44" t="n"/>
+          <t>MODELED dive-transfer band (Klein Bonaire). To be finalized in cascade.</t>
+        </is>
+      </c>
+      <c r="AY6" s="44" t="inlineStr">
+        <is>
+          <t>bonaire dive transfer pool</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -2801,19 +2903,19 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Bonaire</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>Oranjestad Cruise Terminal (Aruba) → Palm Beach resort strip (Aruba)</t>
+          <t>Kralendijk Town Pier (Bonaire) → Harbour Village Marina / dive-resort jetty cluster (Bonaire)</t>
         </is>
       </c>
       <c r="D7" s="31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
@@ -2826,7 +2928,7 @@
         </is>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="I7" s="33">
         <f>60*D7/cruise_kt</f>
@@ -2924,11 +3026,21 @@
         <f>((D7*O7/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D7*O7*VLOOKUP(B7,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG7" s="31" t="n"/>
-      <c r="AH7" s="32" t="n"/>
-      <c r="AI7" s="32" t="n"/>
+      <c r="AG7" s="31" t="n">
+        <v>53850</v>
+      </c>
+      <c r="AH7" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI7" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="AJ7" s="39" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="AK7" s="34">
         <f>IF(AG7="","",AG7*AJ7)</f>
@@ -2973,10 +3085,14 @@
       </c>
       <c r="AX7" s="44" t="inlineStr">
         <is>
-          <t>MODELED premium cruise-shore / resort transfer band. To be finalized in cascade.</t>
-        </is>
-      </c>
-      <c r="AY7" s="44" t="n"/>
+          <t>MODELED short town/cruise→dive-resort transfer. To be finalized in cascade.</t>
+        </is>
+      </c>
+      <c r="AY7" s="44" t="inlineStr">
+        <is>
+          <t>bonaire cruise → dive-resort cluster</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -2986,7 +3102,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -3109,11 +3225,21 @@
         <f>((D8*O8/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D8*O8*VLOOKUP(B8,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG8" s="31" t="n"/>
-      <c r="AH8" s="32" t="n"/>
-      <c r="AI8" s="32" t="n"/>
+      <c r="AG8" s="31" t="n">
+        <v>83489</v>
+      </c>
+      <c r="AH8" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI8" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="AJ8" s="39" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="AK8" s="34">
         <f>IF(AG8="","",AG8*AJ8)</f>
@@ -3161,7 +3287,11 @@
           <t>MODELED premium cruise/town→resort transfer band. To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY8" s="44" t="n"/>
+      <c r="AY8" s="44" t="inlineStr">
+        <is>
+          <t>curacao cruise → resort cluster</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -3171,7 +3301,7 @@
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -3294,11 +3424,21 @@
         <f>((D9*O9/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D9*O9*VLOOKUP(B9,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG9" s="31" t="n"/>
-      <c r="AH9" s="32" t="n"/>
-      <c r="AI9" s="32" t="n"/>
+      <c r="AG9" s="31" t="n">
+        <v>84029</v>
+      </c>
+      <c r="AH9" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI9" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="AJ9" s="39" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="AK9" s="34">
         <f>IF(AG9="","",AG9*AJ9)</f>
@@ -3346,7 +3486,11 @@
           <t>MODELED premium air→resort transfer band. To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY9" s="44" t="n"/>
+      <c r="AY9" s="44" t="inlineStr">
+        <is>
+          <t>curacao airport → south-coast resorts</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -3356,7 +3500,7 @@
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
@@ -3479,11 +3623,21 @@
         <f>((D10*O10/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D10*O10*VLOOKUP(B10,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG10" s="31" t="n"/>
-      <c r="AH10" s="32" t="n"/>
-      <c r="AI10" s="32" t="n"/>
+      <c r="AG10" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AH10" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI10" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="AJ10" s="39" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="AK10" s="34">
         <f>IF(AG10="","",AG10*AJ10)</f>
@@ -3531,7 +3685,11 @@
           <t>MODELED premium seasonal excursion. To be finalized in cascade with season_days.</t>
         </is>
       </c>
-      <c r="AY10" s="44" t="n"/>
+      <c r="AY10" s="44" t="inlineStr">
+        <is>
+          <t>ABC broad-footprint default slice</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -3541,7 +3699,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -3664,11 +3822,21 @@
         <f>((D11*O11/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D11*O11*VLOOKUP(B11,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG11" s="31" t="n"/>
-      <c r="AH11" s="32" t="n"/>
-      <c r="AI11" s="32" t="n"/>
+      <c r="AG11" s="31" t="n">
+        <v>55480</v>
+      </c>
+      <c r="AH11" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI11" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="AJ11" s="39" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="AK11" s="34">
         <f>IF(AG11="","",AG11*AJ11)</f>
@@ -3716,7 +3884,11 @@
           <t>MODELED against the live Divi Divi/EZ Air Curaçao↔Bonaire one-way fare band (~$90-130); sea transfer priced below air. To be finalized in cascade.</t>
         </is>
       </c>
-      <c r="AY11" s="44" t="n"/>
+      <c r="AY11" s="44" t="inlineStr">
+        <is>
+          <t>inter_island_air_substitution_pool Curaçao↔Bonaire high-frequency turboprop</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
